--- a/Result/profitability/6591.xlsx
+++ b/Result/profitability/6591.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM43"/>
+  <dimension ref="A1:AM44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5891,6 +5891,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>6591</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>219</v>
+      </c>
+      <c r="D44" t="n">
+        <v>170</v>
+      </c>
+      <c r="E44" t="n">
+        <v>49</v>
+      </c>
+      <c r="F44" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-30</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-13.49%</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>6</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-24</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.02125</v>
+      </c>
+      <c r="N44" t="n">
+        <v>29.27875</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W44" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X44" t="n">
+        <v>-1.026666666666667</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>-2.130000000000003</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-0.08722358722358736</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>-1.017543859649123</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>-0.4054414510536144</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK44" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
